--- a/CLUDE FILES/תזרים מזומנים מטה סופי.xlsx
+++ b/CLUDE FILES/תזרים מזומנים מטה סופי.xlsx
@@ -3201,7 +3201,7 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>העברה בנקאית – מטה ופתילים (חשבון 902-008892348)</t>
+          <t>הלוואה בערבות מדינה – העברה מחשבון ההלוואה 902-008892348</t>
         </is>
       </c>
       <c r="C25" s="16" t="n"/>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>❓ העברה מחשבון אחר של מטה - לברר מה המקור (הלוואה?)</t>
+          <t>✅ כספי ההלוואה בערבות מדינה (אושר ע"י שמואל 14/10). פיקדון 10% (20,000) הופקד בחיסכון 08/10</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
     <row r="43" ht="16.5" customHeight="1">
       <c r="A43" s="86" t="inlineStr">
         <is>
-          <t>יתרה 14/10: 183,367.64 ₪ - אחרי העברה של 197,850 ב-14/10 מחשבון מטה 902-008892348 (ב-12/10 היה −14,482.36, מינוס). סוף אוקטובר צפוי ב-145,638.41 ₪, לפני תשלומים ממתינים (מאיר הובלות, חומר לבית ירושלמי). ⚠️ אברהם משי קיבל 103,023.44 עבור חן 20124. 20,000 הופקדו בחיסכון כפיקדון להלוואה בערבות מדינה. אייל גולן משולם מחשבון ישר.</t>
+          <t>יתרה 14/10: 183,367.64 ₪ - אחרי קבלת ההלוואה בערבות מדינה 197,850 ב-14/10 (ב-12/10 היה −14,482.36, מינוס). סוף אוקטובר צפוי ב-145,638.41 ₪, לפני תשלומים ממתינים (מאיר הובלות, חומר לבית ירושלמי). ⚠️ אברהם משי קיבל 103,023.44 עבור חן 20124. 20,000 הופקדו בחיסכון כפיקדון להלוואה בערבות מדינה. אייל גולן משולם מחשבון ישר.</t>
         </is>
       </c>
       <c r="B43" s="88" t="n"/>

--- a/CLUDE FILES/תזרים מזומנים מטה סופי.xlsx
+++ b/CLUDE FILES/תזרים מזומנים מטה סופי.xlsx
@@ -3789,7 +3789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="24.75" customWidth="1" style="1" min="1" max="1"/>
@@ -3980,65 +3980,102 @@
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" s="57" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>ערבות מדינה (902-008892348)</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>200000</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>3900</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>כל 28 לחודש</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>28/10/2031 (משוער)</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>≈6.36% שנתי (מחושב מ-60×3,900)</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>התקבלה 14/10/2026 - נכנסו לחשבון 197,850 (2,150 עמלות/ניכויים). 60 תשלומים × 3,900 = 234,000 סה"כ להחזר (34,000 עלות). פיקדון 10% - 20,000 בחיסכון (08/10). תשלום ראשון משוער 28/11/2026 - לאמת מול הבנק</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1">
+      <c r="A8" s="57" t="inlineStr">
         <is>
           <t>סה"כ יתרת הלוואות</t>
         </is>
       </c>
-      <c r="B7" s="49" t="n"/>
-      <c r="C7" s="48" t="n">
-        <v>487139.22</v>
-      </c>
-      <c r="D7" s="49" t="n"/>
-      <c r="E7" s="49" t="n"/>
-      <c r="F7" s="49" t="n"/>
-      <c r="G7" s="49" t="n"/>
-      <c r="H7" s="56" t="n"/>
-    </row>
-    <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="45" t="n"/>
-      <c r="B8" s="42" t="n"/>
-      <c r="C8" s="42" t="n"/>
-      <c r="D8" s="42" t="n"/>
-      <c r="E8" s="42" t="n"/>
-      <c r="F8" s="42" t="n"/>
-      <c r="G8" s="42" t="n"/>
-      <c r="H8" s="43" t="n"/>
+      <c r="B8" s="49" t="n"/>
+      <c r="C8" s="48">
+        <f>SUM(C4:C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="49" t="n"/>
+      <c r="E8" s="49" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="49" t="n"/>
+      <c r="H8" s="56" t="n"/>
     </row>
     <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="84" t="inlineStr">
+      <c r="A9" s="45" t="n"/>
+      <c r="B9" s="42" t="n"/>
+      <c r="C9" s="42" t="n"/>
+      <c r="D9" s="42" t="n"/>
+      <c r="E9" s="42" t="n"/>
+      <c r="F9" s="42" t="n"/>
+      <c r="G9" s="42" t="n"/>
+      <c r="H9" s="43" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1">
+      <c r="A10" s="84" t="inlineStr">
         <is>
           <t>* הסכומים משתנים בהתאם לעדכוני ריבית הפריים. יש לעדכן יתרה מדי חודש.</t>
         </is>
       </c>
-      <c r="B9" s="88" t="n"/>
-      <c r="C9" s="88" t="n"/>
-      <c r="D9" s="88" t="n"/>
-      <c r="E9" s="88" t="n"/>
-      <c r="F9" s="88" t="n"/>
-      <c r="G9" s="88" t="n"/>
-      <c r="H9" s="88" t="n"/>
-    </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="83" t="inlineStr">
+      <c r="B10" s="88" t="n"/>
+      <c r="C10" s="88" t="n"/>
+      <c r="D10" s="88" t="n"/>
+      <c r="E10" s="88" t="n"/>
+      <c r="F10" s="88" t="n"/>
+      <c r="G10" s="88" t="n"/>
+      <c r="H10" s="88" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1">
+      <c r="A11" s="83" t="inlineStr">
         <is>
           <t>* היתרות מבוססות על לוחות הסילוקין המקוריים (מסמכי 106017). התשלומים בפועל סוטים מהלוח בעשרות שקלים בגלל עדכוני פריים, כך שהיתרה בפועל עשויה להיות שונה במעט.</t>
         </is>
       </c>
-      <c r="B10" s="90" t="n"/>
-      <c r="C10" s="90" t="n"/>
-      <c r="D10" s="90" t="n"/>
-      <c r="E10" s="90" t="n"/>
-      <c r="F10" s="90" t="n"/>
-      <c r="G10" s="90" t="n"/>
-      <c r="H10" s="90" t="n"/>
+      <c r="B11" s="90" t="n"/>
+      <c r="C11" s="90" t="n"/>
+      <c r="D11" s="90" t="n"/>
+      <c r="E11" s="90" t="n"/>
+      <c r="F11" s="90" t="n"/>
+      <c r="G11" s="90" t="n"/>
+      <c r="H11" s="90" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
